--- a/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>单据编号</t>
   </si>
@@ -65,6 +65,9 @@
     <t>调入虚拟仓</t>
   </si>
   <si>
+    <t>缺货数量</t>
+  </si>
+  <si>
     <t>订单备注</t>
   </si>
   <si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>{.toVirtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.virtualScarceQty}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1333,7 +1339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -1343,16 +1349,16 @@
     <col min="8" max="8" width="21.375" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="20.875" customWidth="1"/>
-    <col min="11" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="18.75" customWidth="1"/>
-    <col min="15" max="15" width="18.25" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
-    <col min="18" max="18" width="19.375" customWidth="1"/>
+    <col min="11" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="18.75" customWidth="1"/>
+    <col min="16" max="16" width="18.25" customWidth="1"/>
+    <col min="17" max="17" width="16.125" customWidth="1"/>
+    <col min="18" max="18" width="13.5" customWidth="1"/>
+    <col min="19" max="19" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:19">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1407,61 +1413,67 @@
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:18">
+    <row r="2" s="2" customFormat="1" spans="1:19">
       <c r="A2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>单据编号</t>
   </si>
@@ -68,6 +68,9 @@
     <t>缺货数量</t>
   </si>
   <si>
+    <t>是否统计</t>
+  </si>
+  <si>
     <t>订单备注</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>{.virtualScarceQty}</t>
+  </si>
+  <si>
+    <t>{.isStatisticsName}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1339,7 +1345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -1350,15 +1356,15 @@
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="20.875" customWidth="1"/>
     <col min="11" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="17.25" customWidth="1"/>
-    <col min="15" max="15" width="18.75" customWidth="1"/>
-    <col min="16" max="16" width="18.25" customWidth="1"/>
-    <col min="17" max="17" width="16.125" customWidth="1"/>
-    <col min="18" max="18" width="13.5" customWidth="1"/>
-    <col min="19" max="19" width="19.375" customWidth="1"/>
+    <col min="14" max="15" width="17.25" customWidth="1"/>
+    <col min="16" max="16" width="18.75" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="18" max="18" width="16.125" customWidth="1"/>
+    <col min="19" max="19" width="13.5" customWidth="1"/>
+    <col min="20" max="20" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1416,64 +1422,70 @@
       <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:19">
+    <row r="2" s="2" customFormat="1" spans="1:20">
       <c r="A2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>单据编号</t>
   </si>
@@ -65,6 +65,12 @@
     <t>调入虚拟仓</t>
   </si>
   <si>
+    <t>缺货数量</t>
+  </si>
+  <si>
+    <t>是否统计</t>
+  </si>
+  <si>
     <t>订单备注</t>
   </si>
   <si>
@@ -117,6 +123,12 @@
   </si>
   <si>
     <t>{.toVirtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.virtualScarceQty}</t>
+  </si>
+  <si>
+    <t>{.isStatisticsName}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1333,7 +1345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -1343,16 +1355,16 @@
     <col min="8" max="8" width="21.375" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="20.875" customWidth="1"/>
-    <col min="11" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="18.75" customWidth="1"/>
-    <col min="15" max="15" width="18.25" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
-    <col min="18" max="18" width="19.375" customWidth="1"/>
+    <col min="11" max="13" width="20" customWidth="1"/>
+    <col min="14" max="15" width="17.25" customWidth="1"/>
+    <col min="16" max="16" width="18.75" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="18" max="18" width="16.125" customWidth="1"/>
+    <col min="19" max="19" width="13.5" customWidth="1"/>
+    <col min="20" max="20" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1407,61 +1419,73 @@
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:18">
+    <row r="2" s="2" customFormat="1" spans="1:20">
       <c r="A2" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/VirtualWarehouseAllocation.xlsx
@@ -27,66 +27,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>单据编号</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <t>编号</t>
   </si>
   <si>
     <t>状态</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>实体仓</t>
+  </si>
+  <si>
+    <t>实体仓可分配数</t>
+  </si>
+  <si>
+    <t>调出虚拟仓</t>
+  </si>
+  <si>
+    <t>调出仓可用数</t>
+  </si>
+  <si>
+    <t>调入虚拟仓</t>
+  </si>
+  <si>
+    <t>调入仓可用数</t>
+  </si>
+  <si>
+    <t>分配/调拨/取消数量</t>
+  </si>
+  <si>
+    <t>是否缺货</t>
+  </si>
+  <si>
+    <t>缺货数量</t>
+  </si>
+  <si>
+    <t>实体仓实际数量</t>
+  </si>
+  <si>
+    <t>虚拟仓库存</t>
+  </si>
+  <si>
+    <t>同步状态</t>
+  </si>
+  <si>
     <t>同步平台</t>
   </si>
   <si>
-    <t>同步状态</t>
-  </si>
-  <si>
     <t>同步单号</t>
   </si>
   <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>sku名称</t>
-  </si>
-  <si>
-    <t>实体仓</t>
-  </si>
-  <si>
-    <t>调出虚拟仓</t>
-  </si>
-  <si>
-    <t>分配/变更/取消数量</t>
-  </si>
-  <si>
-    <t>调入虚拟仓</t>
-  </si>
-  <si>
-    <t>缺货数量</t>
+    <t>订单备注</t>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
   <si>
     <t>是否统计</t>
   </si>
   <si>
-    <t>订单备注</t>
-  </si>
-  <si>
-    <t>明细备注</t>
-  </si>
-  <si>
     <t>创建人</t>
   </si>
   <si>
     <t>创建时间</t>
   </si>
   <si>
-    <t>修改人</t>
-  </si>
-  <si>
-    <t>修改时间</t>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>更新时间</t>
   </si>
   <si>
     <t>{.code}</t>
@@ -95,46 +113,64 @@
     <t>{.statusName}</t>
   </si>
   <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.skuName}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.unDistributionQty}</t>
+  </si>
+  <si>
+    <t>{.fromVirtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.fromVirtualWarehouseUsableQty}</t>
+  </si>
+  <si>
+    <t>{.toVirtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.toVirtualWarehouseUsableQty}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
+    <t>{.isVirtualScarceStr}</t>
+  </si>
+  <si>
+    <t>{.virtualScarceQty}</t>
+  </si>
+  <si>
+    <t>{.realQty}</t>
+  </si>
+  <si>
+    <t>{.virtualRealQty}</t>
+  </si>
+  <si>
+    <t>{.syncStatusName}</t>
+  </si>
+  <si>
     <t>{.sysTypeName}</t>
   </si>
   <si>
-    <t>{.syncStatusName}</t>
-  </si>
-  <si>
     <t>{.thirdCode}</t>
   </si>
   <si>
-    <t>{.typeName}</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.skuName}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
-  </si>
-  <si>
-    <t>{.fromVirtualWarehouseName}</t>
-  </si>
-  <si>
-    <t>{.qty}</t>
-  </si>
-  <si>
-    <t>{.toVirtualWarehouseName}</t>
-  </si>
-  <si>
-    <t>{.virtualScarceQty}</t>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.isStatisticsName}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
-  </si>
-  <si>
-    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1345,33 +1381,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
-    <col min="8" max="8" width="21.375" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="20.875" customWidth="1"/>
-    <col min="11" max="13" width="20" customWidth="1"/>
-    <col min="14" max="15" width="17.25" customWidth="1"/>
-    <col min="16" max="16" width="18.75" customWidth="1"/>
-    <col min="17" max="17" width="18.25" customWidth="1"/>
-    <col min="18" max="18" width="16.125" customWidth="1"/>
-    <col min="19" max="19" width="13.5" customWidth="1"/>
-    <col min="20" max="20" width="19.375" customWidth="1"/>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="21.375" customWidth="1"/>
+    <col min="6" max="7" width="17" customWidth="1"/>
+    <col min="8" max="9" width="20.875" customWidth="1"/>
+    <col min="10" max="16" width="20" customWidth="1"/>
+    <col min="17" max="19" width="19.75" customWidth="1"/>
+    <col min="20" max="20" width="17.25" customWidth="1"/>
+    <col min="21" max="21" width="18.75" customWidth="1"/>
+    <col min="22" max="22" width="17.25" customWidth="1"/>
+    <col min="23" max="23" width="18.25" customWidth="1"/>
+    <col min="24" max="24" width="16.125" customWidth="1"/>
+    <col min="25" max="25" width="13.5" customWidth="1"/>
+    <col min="26" max="26" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:26">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
@@ -1380,7 +1418,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1425,67 +1463,103 @@
       <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:20">
+    <row r="2" s="2" customFormat="1" spans="1:26">
       <c r="A2" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
